--- a/Configure.xlsx
+++ b/Configure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A01 FIVE\PROJECTS\uninterruptible-power-supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99038716-27D0-4A4E-AC12-53ED59BE2010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48001F2B-0382-494E-916D-B6A7D6788444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5F64C27A-1FDD-41D1-8BF6-AC244198F7E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{5F64C27A-1FDD-41D1-8BF6-AC244198F7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Electrical Equipment" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
-  <si>
-    <t>Phân Xưởng</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>P, kW</t>
   </si>
@@ -98,20 +95,6 @@
   </si>
   <si>
     <t>Máy số</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">cosφ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>∑</t>
-    </r>
   </si>
   <si>
     <t>TPP 01</t>
@@ -185,6 +168,33 @@
   <si>
     <t>MCCB 06</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">cosφ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>∑</t>
+    </r>
+  </si>
+  <si>
+    <t>MBA, kVA</t>
+  </si>
+  <si>
+    <t>Phân xưởng</t>
+  </si>
 </sst>
 </file>
 
@@ -193,7 +203,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,10 +231,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -241,7 +258,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -301,11 +318,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -327,73 +357,83 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1374,8 +1414,8 @@
       <xdr:rowOff>32657</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="243785" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1457,7 +1497,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1963,8 +2003,8 @@
       <xdr:rowOff>43543</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="243785" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -2046,7 +2086,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -2106,13 +2146,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>119269</xdr:colOff>
+      <xdr:colOff>137199</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>109330</xdr:rowOff>
+      <xdr:rowOff>154154</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="343748" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -2126,7 +2166,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4890052" y="109330"/>
+              <a:off x="5444305" y="154154"/>
               <a:ext cx="343748" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2200,7 +2240,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -2214,7 +2254,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4890052" y="109330"/>
+              <a:off x="5444305" y="154154"/>
               <a:ext cx="343748" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2242,6 +2282,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2267,11 +2308,11 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>218661</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>102705</xdr:rowOff>
+      <xdr:rowOff>138564</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="247055" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2285,7 +2326,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6208644" y="102705"/>
+              <a:off x="6762896" y="138564"/>
               <a:ext cx="247055" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2353,7 +2394,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2367,7 +2408,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6208644" y="102705"/>
+              <a:off x="6762896" y="138564"/>
               <a:ext cx="247055" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2395,6 +2436,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2412,13 +2454,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>212035</xdr:colOff>
+      <xdr:colOff>221000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>109331</xdr:rowOff>
+      <xdr:rowOff>118296</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="247312" cy="182614"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -2432,7 +2474,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5592418" y="109331"/>
+              <a:off x="6146671" y="118296"/>
               <a:ext cx="247312" cy="182614"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2500,7 +2542,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -2514,7 +2556,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5592418" y="109331"/>
+              <a:off x="6146671" y="118296"/>
               <a:ext cx="247312" cy="182614"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2542,6 +2584,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2559,13 +2602,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>106019</xdr:colOff>
+      <xdr:colOff>97054</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>112644</xdr:rowOff>
+      <xdr:rowOff>148503</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="428259" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="415114" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -2579,8 +2622,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6705602" y="112644"/>
-              <a:ext cx="428259" cy="172227"/>
+              <a:off x="7878419" y="148503"/>
+              <a:ext cx="415114" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2630,7 +2673,7 @@
                         <a:rPr lang="en-US" sz="1100" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
-                        <m:t>𝑡𝑡</m:t>
+                        <m:t>𝑁</m:t>
                       </m:r>
                     </m:sub>
                   </m:sSub>
@@ -2644,7 +2687,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -2658,8 +2701,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6705602" y="112644"/>
-              <a:ext cx="428259" cy="172227"/>
+              <a:off x="7878419" y="148503"/>
+              <a:ext cx="415114" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2686,12 +2729,11 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑃_𝑡𝑡</a:t>
+                <a:t>𝑃_𝑁</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="1100"/>
@@ -3595,13 +3637,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>125896</xdr:colOff>
+      <xdr:colOff>152790</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>86139</xdr:rowOff>
+      <xdr:rowOff>139927</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="346698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -3615,7 +3657,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9773479" y="86139"/>
+              <a:off x="11026978" y="139927"/>
               <a:ext cx="346698" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3689,7 +3731,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -3703,7 +3745,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9773479" y="86139"/>
+              <a:off x="11026978" y="139927"/>
               <a:ext cx="346698" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3755,19 +3797,150 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>139148</xdr:colOff>
+      <xdr:colOff>115702</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>106017</xdr:rowOff>
+      <xdr:rowOff>153254</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="373820" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="437749" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69A4BDDE-F364-42E6-9B86-C0911F3AAEBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7278502" y="153254"/>
+          <a:ext cx="437749" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>P</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="el-GR" sz="1100"/>
+            <a:t> ∑</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>, kW</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>19879</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41031</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="517642" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C88804FB-B73B-4D5A-AE47-31E72121B7F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12780448" y="41031"/>
+          <a:ext cx="517642" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> XN, kW</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>32657</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="693331" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="TextBox 19">
+            <xdr:cNvPr id="22" name="TextBox 21">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69A4BDDE-F364-42E6-9B86-C0911F3AAEBA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD9304FF-4626-4786-8D5B-36D14EB1AC73}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3775,8 +3948,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6738731" y="106017"/>
-              <a:ext cx="373820" cy="172227"/>
+              <a:off x="12771455" y="261257"/>
+              <a:ext cx="693331" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3823,166 +3996,6 @@
                           <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>𝑃</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑑𝑚</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>∑</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="TextBox 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69A4BDDE-F364-42E6-9B86-C0911F3AAEBA}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6738731" y="106017"/>
-              <a:ext cx="373820" cy="172227"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑃_𝑑𝑚</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>∑</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>19879</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="467692" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C88804FB-B73B-4D5A-AE47-31E72121B7F2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4790662" y="5194852"/>
-              <a:ext cx="467692" cy="172227"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
                           <m:t>𝑆</m:t>
                         </m:r>
                       </m:e>
@@ -3991,7 +4004,7 @@
                           <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>𝑑𝑚</m:t>
+                          <m:t>𝑁</m:t>
                         </m:r>
                       </m:sub>
                     </m:sSub>
@@ -4001,159 +4014,17 @@
                       </a:rPr>
                       <m:t>𝑋𝑁</m:t>
                     </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100" b="0"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C88804FB-B73B-4D5A-AE47-31E72121B7F2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4790662" y="5194852"/>
-              <a:ext cx="467692" cy="172227"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑆_𝑑𝑚 𝑋𝑁</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100" b="0"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>10886</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>32657</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="397288" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22" name="TextBox 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD9304FF-4626-4786-8D5B-36D14EB1AC73}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12801600" y="261257"/>
-              <a:ext cx="397288" cy="172227"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑆</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡𝑡</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>𝑋𝑁</m:t>
+                      <m:t>, </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑘𝑉𝐴</m:t>
                     </m:r>
                   </m:oMath>
                 </m:oMathPara>
@@ -4177,8 +4048,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12801600" y="261257"/>
-              <a:ext cx="397288" cy="172227"/>
+              <a:off x="12771455" y="261257"/>
+              <a:ext cx="693331" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4210,7 +4081,7 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑆_𝑡𝑡 𝑋𝑁</a:t>
+                <a:t>𝑆_𝑁 𝑋𝑁, 𝑘𝑉𝐴</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100" b="0"/>
             </a:p>
@@ -4222,12 +4093,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>10885</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>21772</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="441531" cy="172227"/>
+    <xdr:ext cx="514500" cy="184731"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -4243,8 +4114,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12801599" y="478972"/>
-              <a:ext cx="441531" cy="172227"/>
+              <a:off x="12771454" y="478972"/>
+              <a:ext cx="514500" cy="184731"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4300,6 +4171,12 @@
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑠𝑑</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>∑</m:t>
                         </m:r>
                       </m:sub>
                     </m:sSub>
@@ -4331,8 +4208,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12801599" y="478972"/>
-              <a:ext cx="441531" cy="172227"/>
+              <a:off x="12771454" y="478972"/>
+              <a:ext cx="514500" cy="184731"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4364,7 +4241,7 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝐾_𝑠𝑑 𝑋𝑁</a:t>
+                <a:t>𝐾_(𝑠𝑑∑) 𝑋𝑁</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -4376,14 +4253,14 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>21771</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>33130</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="444802" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -4471,7 +4348,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -4530,12 +4407,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>10886</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>28470</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>21771</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="401200" cy="172227"/>
+    <xdr:ext cx="302519" cy="172227"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -4551,8 +4428,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12801600" y="1393371"/>
-              <a:ext cx="401200" cy="172227"/>
+              <a:off x="12789039" y="1393371"/>
+              <a:ext cx="302519" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4580,45 +4457,23 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0"/>
+                <a:t>P</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+                <a:t> </a:t>
+              </a:r>
               <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑃</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡𝑡</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑋𝑁</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:r>
+                    <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    </a:rPr>
+                    <m:t>𝑋𝑁</m:t>
+                  </m:r>
+                </m:oMath>
               </a14:m>
               <a:endParaRPr lang="en-US" sz="1100" b="0"/>
             </a:p>
@@ -4639,8 +4494,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12801600" y="1393371"/>
-              <a:ext cx="401200" cy="172227"/>
+              <a:off x="12789039" y="1393371"/>
+              <a:ext cx="302519" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4669,10 +4524,18 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0"/>
+                <a:t>P</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑃_𝑡𝑡 𝑋𝑁</a:t>
+                <a:t>𝑋𝑁</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100" b="0"/>
             </a:p>
@@ -4684,14 +4547,14 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>17584</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>13253</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="419794" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="324512" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -4705,8 +4568,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4770783" y="6506818"/>
-              <a:ext cx="419794" cy="172227"/>
+              <a:off x="12778153" y="1613453"/>
+              <a:ext cx="324512" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4734,52 +4597,30 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0"/>
+                <a:t>Q</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+                <a:t> </a:t>
+              </a:r>
               <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑄</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡𝑡</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑋𝑁</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:r>
+                    <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    </a:rPr>
+                    <m:t>𝑋𝑁</m:t>
+                  </m:r>
+                </m:oMath>
               </a14:m>
               <a:endParaRPr lang="en-US" sz="1100" b="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -4793,8 +4634,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4770783" y="6506818"/>
-              <a:ext cx="419794" cy="172227"/>
+              <a:off x="12778153" y="1613453"/>
+              <a:ext cx="324512" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4823,356 +4664,20 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑄_𝑡𝑡 𝑋𝑁</a:t>
+                <a:rPr lang="en-US" sz="1100" b="0"/>
+                <a:t>Q</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="1100" b="0"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>13252</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>92766</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="601255" cy="176972"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="33" name="TextBox 32">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCB282DE-F4D2-403C-8297-410DCE2E9FB5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10864132" y="92766"/>
-              <a:ext cx="601255" cy="176972"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐹</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡h𝑎𝑛h</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑐</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>á</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑖</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="33" name="TextBox 32">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCB282DE-F4D2-403C-8297-410DCE2E9FB5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10864132" y="92766"/>
-              <a:ext cx="601255" cy="176972"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+                <a:t> </a:t>
+              </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝐹_(𝑡ℎ𝑎𝑛ℎ 𝑐á𝑖)</a:t>
+                <a:t>𝑋𝑁</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>79513</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>92766</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="506357" cy="186269"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="34" name="TextBox 33">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34F36DFC-4A92-4457-B522-F597DF8E09E8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11555896" y="92766"/>
-              <a:ext cx="506357" cy="186269"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐹</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑑</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>â</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑦</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t> đẫ</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑛</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="34" name="TextBox 33">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34F36DFC-4A92-4457-B522-F597DF8E09E8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11555896" y="92766"/>
-              <a:ext cx="506357" cy="186269"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐹_(𝑑â𝑦 đẫ𝑛)</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" b="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5188,8 +4693,8 @@
       <xdr:rowOff>26504</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="414922" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="TextBox 34">
@@ -5264,7 +4769,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="TextBox 34">
@@ -5624,9 +5129,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>708991</xdr:colOff>
+      <xdr:colOff>883163</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>6626</xdr:rowOff>
+      <xdr:rowOff>17512</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="414922" cy="172227"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -5644,7 +5149,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="708991" y="4830417"/>
+              <a:off x="883163" y="5961112"/>
               <a:ext cx="414922" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5719,7 +5224,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="708991" y="4830417"/>
+              <a:off x="883163" y="5961112"/>
               <a:ext cx="414922" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5771,13 +5276,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>8965</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>13252</xdr:rowOff>
+      <xdr:rowOff>31181</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="414922" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="39" name="TextBox 38">
@@ -5791,7 +5296,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="715617" y="5764695"/>
+              <a:off x="896471" y="7256734"/>
               <a:ext cx="414922" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5852,7 +5357,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="39" name="TextBox 38">
@@ -5866,7 +5371,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="715617" y="5764695"/>
+              <a:off x="896471" y="7256734"/>
               <a:ext cx="414922" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6064,12 +5569,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>21773</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>45220</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>26507</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="383951" cy="172227"/>
+    <xdr:ext cx="243978" cy="172227"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -6085,8 +5590,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12812487" y="1855307"/>
-              <a:ext cx="383951" cy="172227"/>
+              <a:off x="12805789" y="1855307"/>
+              <a:ext cx="243978" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6114,54 +5619,26 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0"/>
+                <a:t>I</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+                <a:t> </a:t>
+              </a:r>
               <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐼</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡𝑡</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>XN</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:r>
+                    <m:rPr>
+                      <m:sty m:val="p"/>
+                    </m:rPr>
+                    <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    </a:rPr>
+                    <m:t>XN</m:t>
+                  </m:r>
+                </m:oMath>
               </a14:m>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -6182,8 +5659,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12812487" y="1855307"/>
-              <a:ext cx="383951" cy="172227"/>
+              <a:off x="12805789" y="1855307"/>
+              <a:ext cx="243978" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6212,10 +5689,18 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0"/>
+                <a:t>I</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝐼_𝑡𝑡  XN</a:t>
+                <a:t>XN</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -6227,14 +5712,14 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>13252</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>28401</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="512897" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="42" name="TextBox 41">
@@ -6331,7 +5816,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="42" name="TextBox 41">
@@ -6390,7 +5875,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
@@ -6568,7 +6053,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -6716,7 +6201,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
@@ -6864,7 +6349,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -7012,7 +6497,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -7160,7 +6645,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -7308,7 +6793,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -7456,7 +6941,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -7604,7 +7089,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
@@ -7771,6 +7256,409 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐼_𝑛  PX, kA</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>38518</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="722762" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="45" name="TextBox 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3282B280-7E8E-4540-BC79-8E40A63C9229}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12771455" y="4839118"/>
+              <a:ext cx="722762" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡𝑏</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑋𝑁</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>, </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑘𝑉𝐴</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="45" name="TextBox 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3282B280-7E8E-4540-BC79-8E40A63C9229}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12771455" y="4839118"/>
+              <a:ext cx="722762" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆_𝑡𝑏 𝑋𝑁, 𝑘𝑉𝐴</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>40194</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>32656</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="211533" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAAE7469-8F1A-426C-BA3A-EDF1BE88F9D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12800763" y="5061856"/>
+          <a:ext cx="211533" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>Kdk</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="649985" cy="182614"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="47" name="TextBox 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE8C91C9-BCC2-4A49-8880-D5429ECBB664}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12774706" y="5593976"/>
+              <a:ext cx="649985" cy="182614"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑞𝑢</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>á </m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>ả</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑋𝑁</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="47" name="TextBox 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE8C91C9-BCC2-4A49-8880-D5429ECBB664}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12774706" y="5593976"/>
+              <a:ext cx="649985" cy="182614"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘_(𝑞𝑢á 𝑡ả𝑖) 𝑋𝑁</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -8097,39 +7985,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="C1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32" t="s">
+      <c r="J1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="K1" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="5">
         <v>316.07</v>
@@ -8147,24 +8035,24 @@
         <v>65</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5">
         <v>316.07</v>
@@ -8182,24 +8070,24 @@
         <v>65</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5">
         <v>316.07</v>
@@ -8217,24 +8105,24 @@
         <v>65</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5">
         <v>110.17</v>
@@ -8252,24 +8140,24 @@
         <v>36</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5">
         <v>113.43</v>
@@ -8287,24 +8175,24 @@
         <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="5">
         <v>103.75</v>
@@ -8322,24 +8210,24 @@
         <v>36</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="5">
         <v>103.71</v>
@@ -8357,24 +8245,24 @@
         <v>36</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5">
         <v>60.74</v>
@@ -8392,24 +8280,24 @@
         <v>36</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5">
         <v>99.26</v>
@@ -8427,13 +8315,13 @@
         <v>36</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8446,7 +8334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1AC3892-BAAE-4B81-9134-26B00DE6651D}">
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -8456,1817 +8344,1726 @@
     <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
     <col min="15" max="21" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.109375" customWidth="1"/>
-    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.44140625" customWidth="1"/>
+    <col min="24" max="24" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19" t="s">
+    <row r="1" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="23" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="S1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="24" t="s">
+      <c r="U1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="V1" s="21"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="10">
+      <c r="V1" s="32"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="9">
         <f>T3+T8+T13+T18+T23+T28</f>
         <v>386.75392951580517</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="27">
+    <row r="2" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37">
         <v>1</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="37">
         <v>2</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="37">
         <v>3</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="37">
         <v>4</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="37">
         <v>5</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="37">
         <v>6</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="37">
         <v>7</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="37">
         <v>8</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="37">
         <v>9</v>
       </c>
-      <c r="L2" s="27">
+      <c r="L2" s="37">
         <v>10</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="10">
-        <f>Z3*Z1</f>
-        <v>218.98307727369971</v>
+      <c r="M2" s="32"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="9">
+        <f>X4*X1</f>
+        <v>287.47524089120463</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
+    <row r="3" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11">
+      <c r="B3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8">
         <v>5.6</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="8">
         <v>4.5</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="8">
         <v>10</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="8">
         <v>7.5</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="8">
         <v>10</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="8">
         <v>2.8</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="8">
         <v>5</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="8">
         <v>7.5</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="13">
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="16">
         <f>(C3*C4+D3*D4+E3*E4+F3*F4+G3*G4+H3*H4+I3*I4+J3*J4)/(C3+D3+E3+F3+G3+H3+I3+J3)</f>
         <v>0.59482041587901702</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="19">
         <v>8</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="16">
         <f>M3+(1-M3)/SQRT(N3)</f>
         <v>0.73807303164416316</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="16">
         <f>C3+D3+E3+F3+G3+H3+I3+J3+K3+L3</f>
         <v>52.9</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="16">
         <f>O3*P3</f>
         <v>39.044063373976229</v>
       </c>
-      <c r="R3" s="13">
+      <c r="R3" s="16">
         <f>(C3*C5+D3*D5+E3*E5+F3*F5+G3*G5+H3*H5+I3*I5+J3*J5+K3*K5+L3*L5)/P3</f>
         <v>0.7351606805293005</v>
       </c>
-      <c r="S3" s="13">
+      <c r="S3" s="16">
         <f>SQRT(1-POWER(R3,2))/R3</f>
         <v>0.92210167182353608</v>
       </c>
-      <c r="T3" s="13">
+      <c r="T3" s="16">
         <f>P3/R3</f>
         <v>71.957058369760873</v>
       </c>
-      <c r="U3" s="13">
+      <c r="U3" s="16">
         <f>P3*S3</f>
         <v>48.779178439465056</v>
       </c>
-      <c r="V3" s="13">
+      <c r="V3" s="16">
         <f>C6+D6+E6+F6+G6+H6+I6+J6+K6+L6</f>
         <v>110.17409271719751</v>
       </c>
-      <c r="W3" s="13">
-        <f>V3/1.8</f>
-        <v>61.207829287331947</v>
-      </c>
-      <c r="X3" s="13">
-        <f>V3/2.7</f>
-        <v>40.805219524887967</v>
-      </c>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="10">
-        <f>(T3*M3+T8*M8+T13*M13+T18*M18+T23*M23+T28*M28)/Z1</f>
+      <c r="W3" s="22"/>
+      <c r="X3" s="9">
+        <f>(T3*M3+T8*M8+T13*M13+T18*M18+T23*M23+T28*M28)/X1</f>
         <v>0.56620776302869003</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11">
+    <row r="4" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="20"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="8">
         <v>0.65</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="8">
         <v>0.62</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="8">
         <v>0.46</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="8">
         <v>0.68</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="8">
         <v>0.87</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="8">
         <v>0.83</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="8">
         <v>0.38</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="10">
-        <f>Z3+((1-Z3)/SQRT(6))</f>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="9">
+        <f>X3+((1-X3)/SQRT(6))</f>
         <v>0.7433027021887223</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="11">
+    <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="20"/>
+      <c r="B5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
         <v>0.78</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="8">
         <v>0.81</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="8">
         <v>0.68</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="8">
         <v>0.64</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="8">
         <v>0.79</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="8">
         <v>0.84</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="8">
         <v>0.77</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="8">
         <v>0.69</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z5" s="10">
-        <f>(T3*R3+T8*R8+T13*R13+T18*R18+T23*R23+T28*R28)/Z1</f>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="X5" s="9">
+        <f>(T3*R3+T8*R8+T13*R13+T18*R18+T23*R23+T28*R28)/X1</f>
         <v>0.75060646536530296</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="14"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11">
+    <row r="6" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="20"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="8">
         <f>C3/(SQRT(3)*0.38*C5)</f>
         <v>10.908102251895762</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="8">
         <f t="shared" ref="D6:J6" si="0">D3/(SQRT(3)*0.38*D5)</f>
         <v>8.4407934092050549</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="8">
         <f t="shared" si="0"/>
         <v>22.343276671425144</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="8">
         <f t="shared" si="0"/>
         <v>17.804798597541915</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="8">
         <f t="shared" si="0"/>
         <v>19.23218751464443</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>5.0644760455230333</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="8">
         <f t="shared" si="0"/>
         <v>9.8658624263435701</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="8">
         <f t="shared" si="0"/>
         <v>16.514595800618586</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z6" s="10">
-        <f>SQRT(1-POWER(Z5,2))</f>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="9">
+        <f>SQRT(1-POWER(X5,2))</f>
         <v>0.66074952451878943</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11">
+    <row r="7" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="21"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="8">
         <f>C6/2.7</f>
         <v>4.0400378710725047</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="8">
         <f t="shared" ref="D7:J7" si="1">D6/2.7</f>
         <v>3.1262197811870571</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="8">
         <f t="shared" si="1"/>
         <v>8.2752876560833855</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="8">
         <f t="shared" si="1"/>
         <v>6.5943698509414492</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="8">
         <f t="shared" si="1"/>
         <v>7.1230324128312699</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <f t="shared" si="1"/>
         <v>1.8757318687122344</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="8">
         <f t="shared" si="1"/>
         <v>3.6540231208679885</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="8">
         <f t="shared" si="1"/>
         <v>6.1165169631920691</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="10">
-        <f>Z2*Z5</f>
-        <v>164.37011360722875</v>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="9">
+        <f>X2*X5</f>
+        <v>215.78077444538613</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+    <row r="8" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="B8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8">
         <v>10</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="8">
         <v>2.8</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>4.5</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="8">
         <v>6.3</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="8">
         <v>7.2</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="8">
         <v>6</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="8">
         <v>5.6</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="8">
         <v>4.5</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="8">
         <v>10</v>
       </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13">
+      <c r="L8" s="8"/>
+      <c r="M8" s="16">
         <f>(C8*C9+D8*D9+E8*E9+F8*F9+G8*G9+H8*H9+I8*I9+J8*J9+K8*K9)/(C8+D8+E8+F8+G8+H8+I8+J8+K8)</f>
         <v>0.52497363796133578</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="19">
         <v>9</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="16">
         <f t="shared" ref="O8" si="2">M8+(1-M8)/SQRT(N8)</f>
         <v>0.68331575864089056</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="16">
         <f t="shared" ref="P8" si="3">C8+D8+E8+F8+G8+H8+I8+J8+K8+L8</f>
         <v>56.9</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="16">
         <f t="shared" ref="Q8" si="4">O8*P8</f>
         <v>38.88066666666667</v>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="16">
         <f t="shared" ref="R8" si="5">(C8*C10+D8*D10+E8*E10+F8*F10+G8*G10+H8*H10+I8*I10+J8*J10+K8*K10+L8*L10)/P8</f>
         <v>0.76625659050966621</v>
       </c>
-      <c r="S8" s="13">
+      <c r="S8" s="16">
         <f t="shared" ref="S8" si="6">SQRT(1-POWER(R8,2))/R8</f>
         <v>0.83853725431541892</v>
       </c>
-      <c r="T8" s="13">
+      <c r="T8" s="16">
         <f t="shared" ref="T8" si="7">P8/R8</f>
         <v>74.257110091743101</v>
       </c>
-      <c r="U8" s="13">
+      <c r="U8" s="16">
         <f t="shared" ref="U8" si="8">P8*S8</f>
         <v>47.712769770547332</v>
       </c>
-      <c r="V8" s="13">
+      <c r="V8" s="16">
         <f>C11+D11+E11+F11+G11+H11+I11+J11+K11+L11</f>
         <v>113.43415205722086</v>
       </c>
-      <c r="W8" s="13">
-        <f t="shared" ref="W8" si="9">V8/1.8</f>
-        <v>63.018973365122697</v>
-      </c>
-      <c r="X8" s="13">
-        <f t="shared" ref="X8" si="10">V8/2.7</f>
-        <v>42.012648910081793</v>
-      </c>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="10">
-        <f>Z2*Z6</f>
-        <v>144.69296418625839</v>
+      <c r="W8" s="22"/>
+      <c r="X8" s="9">
+        <f>X2*X6</f>
+        <v>189.94912872978793</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11">
+    <row r="9" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="20"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="8">
         <v>0.43</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <v>0.54</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <v>0.47</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="8">
         <v>0.49</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="8">
         <v>0.67</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="8">
         <v>0.65</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="8">
         <v>0.62</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="8">
         <v>0.46</v>
       </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="10">
-        <f>Z2/(SQRT(3)*0.4)</f>
-        <v>316.07484652985784</v>
+      <c r="L9" s="8"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22">
+        <f>X2/(SQRT(3)*22)</f>
+        <v>7.5442685324495233</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="14"/>
-      <c r="B10" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="11">
+    <row r="10" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
+      <c r="B10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
         <v>0.74</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="8">
         <v>0.69</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="8">
         <v>0.82</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <v>0.83</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="8">
         <v>0.83</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="8">
         <v>0.76</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="8">
         <v>0.78</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="8">
         <v>0.81</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="8">
         <v>0.68</v>
       </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="10">
-        <f>Z9/1.8</f>
-        <v>175.59713696103213</v>
+      <c r="L10" s="8"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22">
+        <f>X9/1.2</f>
+        <v>6.2868904437079367</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="14"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11">
-        <f t="shared" ref="C11:K11" si="11">C8/(SQRT(3)*0.38*C10)</f>
+    <row r="11" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="20"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="8">
+        <f t="shared" ref="C11:K11" si="9">C8/(SQRT(3)*0.38*C10)</f>
         <v>20.531659644012297</v>
       </c>
-      <c r="D11" s="11">
-        <f t="shared" si="11"/>
+      <c r="D11" s="8">
+        <f t="shared" si="9"/>
         <v>6.1654490988976054</v>
       </c>
-      <c r="E11" s="11">
-        <f t="shared" si="11"/>
+      <c r="E11" s="8">
+        <f t="shared" si="9"/>
         <v>8.3378569042147497</v>
       </c>
-      <c r="F11" s="11">
-        <f t="shared" si="11"/>
+      <c r="F11" s="8">
+        <f t="shared" si="9"/>
         <v>11.532361115709076</v>
       </c>
-      <c r="G11" s="11">
-        <f t="shared" si="11"/>
+      <c r="G11" s="8">
+        <f t="shared" si="9"/>
         <v>13.179841275096088</v>
       </c>
-      <c r="H11" s="11">
-        <f t="shared" si="11"/>
+      <c r="H11" s="8">
+        <f t="shared" si="9"/>
         <v>11.994811686765081</v>
       </c>
-      <c r="I11" s="11">
-        <f t="shared" si="11"/>
+      <c r="I11" s="8">
+        <f t="shared" si="9"/>
         <v>10.908102251895762</v>
       </c>
-      <c r="J11" s="11">
-        <f t="shared" si="11"/>
+      <c r="J11" s="8">
+        <f t="shared" si="9"/>
         <v>8.4407934092050549</v>
       </c>
-      <c r="K11" s="11">
-        <f t="shared" si="11"/>
+      <c r="K11" s="8">
+        <f t="shared" si="9"/>
         <v>22.343276671425144</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="10">
-        <f>POWER(0.4, 2)/Z1</f>
-        <v>4.136997397810833E-4</v>
+      <c r="L11" s="8"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="9">
+        <f>POWER(0.4, 2)/180</f>
+        <v>8.8888888888888904E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11">
-        <f t="shared" ref="C12:K12" si="12">C11/2.7</f>
+    <row r="12" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A12" s="21"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="8">
+        <f t="shared" ref="C12:K12" si="10">C11/2.7</f>
         <v>7.6043183866712205</v>
       </c>
-      <c r="D12" s="11">
-        <f t="shared" si="12"/>
+      <c r="D12" s="8">
+        <f t="shared" si="10"/>
         <v>2.2834996662583724</v>
       </c>
-      <c r="E12" s="11">
-        <f t="shared" si="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="10"/>
         <v>3.0880951497091664</v>
       </c>
-      <c r="F12" s="11">
-        <f t="shared" si="12"/>
+      <c r="F12" s="8">
+        <f t="shared" si="10"/>
         <v>4.2712448576700277</v>
       </c>
-      <c r="G12" s="11">
-        <f t="shared" si="12"/>
+      <c r="G12" s="8">
+        <f t="shared" si="10"/>
         <v>4.8814226944800323</v>
       </c>
-      <c r="H12" s="11">
-        <f t="shared" si="12"/>
+      <c r="H12" s="8">
+        <f t="shared" si="10"/>
         <v>4.4425228469500295</v>
       </c>
-      <c r="I12" s="11">
-        <f t="shared" si="12"/>
+      <c r="I12" s="8">
+        <f t="shared" si="10"/>
         <v>4.0400378710725047</v>
       </c>
-      <c r="J12" s="11">
-        <f t="shared" si="12"/>
+      <c r="J12" s="8">
+        <f t="shared" si="10"/>
         <v>3.1262197811870571</v>
       </c>
-      <c r="K12" s="11">
-        <f t="shared" si="12"/>
+      <c r="K12" s="8">
+        <f t="shared" si="10"/>
         <v>8.2752876560833855</v>
       </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="10">
+      <c r="L12" s="8"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="9">
         <v>7.7749999999999998E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
+    <row r="13" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
         <v>3</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11">
+      <c r="B13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="8">
         <v>4.5</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="8">
         <v>6.3</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <v>10</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="8">
         <v>4</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="8">
         <v>10</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="8">
         <v>4.5</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="8">
         <v>3</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="13">
-        <f t="shared" ref="M13" si="13">(C13*C14+D13*D14+E13*E14+F13*F14+G13*G14+H13*H14+I13*I14+J13*J14)/(C13+D13+E13+F13+G13+H13+I13+J13)</f>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="16">
+        <f t="shared" ref="M13" si="11">(C13*C14+D13*D14+E13*E14+F13*F14+G13*G14+H13*H14+I13*I14+J13*J14)/(C13+D13+E13+F13+G13+H13+I13+J13)</f>
         <v>0.52767716535433073</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="19">
         <v>8</v>
       </c>
-      <c r="O13" s="13">
-        <f t="shared" ref="O13" si="14">M13+(1-M13)/SQRT(N13)</f>
+      <c r="O13" s="16">
+        <f t="shared" ref="O13" si="12">M13+(1-M13)/SQRT(N13)</f>
         <v>0.69466850499793331</v>
       </c>
-      <c r="P13" s="13">
-        <f t="shared" ref="P13" si="15">C13+D13+E13+F13+G13+H13+I13+J13+K13+L13</f>
+      <c r="P13" s="16">
+        <f t="shared" ref="P13" si="13">C13+D13+E13+F13+G13+H13+I13+J13+K13+L13</f>
         <v>50.8</v>
       </c>
-      <c r="Q13" s="13">
-        <f t="shared" ref="Q13" si="16">O13*P13</f>
+      <c r="Q13" s="16">
+        <f t="shared" ref="Q13" si="14">O13*P13</f>
         <v>35.28916005389501</v>
       </c>
-      <c r="R13" s="13">
-        <f t="shared" ref="R13" si="17">(C13*C15+D13*D15+E13*E15+F13*F15+G13*G15+H13*H15+I13*I15+J13*J15+K13*K15+L13*L15)/P13</f>
+      <c r="R13" s="16">
+        <f t="shared" ref="R13" si="15">(C13*C15+D13*D15+E13*E15+F13*F15+G13*G15+H13*H15+I13*I15+J13*J15+K13*K15+L13*L15)/P13</f>
         <v>0.74840551181102377</v>
       </c>
-      <c r="S13" s="13">
-        <f t="shared" ref="S13" si="18">SQRT(1-POWER(R13,2))/R13</f>
+      <c r="S13" s="16">
+        <f t="shared" ref="S13" si="16">SQRT(1-POWER(R13,2))/R13</f>
         <v>0.88620596198464063</v>
       </c>
-      <c r="T13" s="13">
-        <f t="shared" ref="T13" si="19">P13/R13</f>
+      <c r="T13" s="16">
+        <f t="shared" ref="T13" si="17">P13/R13</f>
         <v>67.877640127304758</v>
       </c>
-      <c r="U13" s="13">
-        <f t="shared" ref="U13" si="20">P13*S13</f>
+      <c r="U13" s="16">
+        <f t="shared" ref="U13" si="18">P13*S13</f>
         <v>45.019262868819744</v>
       </c>
-      <c r="V13" s="13">
+      <c r="V13" s="16">
         <f>C16+D16+E16+F16+G16+H16+I16+J16+K16+L16</f>
         <v>103.75412931705264</v>
       </c>
-      <c r="W13" s="13">
-        <f t="shared" ref="W13" si="21">V13/1.8</f>
-        <v>57.641182953918133</v>
-      </c>
-      <c r="X13" s="13">
-        <f t="shared" ref="X13" si="22">V13/2.7</f>
-        <v>38.427455302612088</v>
-      </c>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="10">
+      <c r="W13" s="26"/>
+      <c r="X13" s="9">
         <v>1.5994999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11">
+    <row r="14" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="20"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="8">
         <v>0.62</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="8">
         <v>0.41</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="8">
         <v>0.66</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="8">
         <v>0.37</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="8">
         <v>0.67</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="8">
         <v>0.75</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="10">
-        <f>SQRT(POWER(Z12,2)+POWER(Z11+Z13, 2))</f>
-        <v>1.8157534308112754E-2</v>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="9">
+        <f>SQRT(POWER(X12,2)+POWER(X11+X13, 2))</f>
+        <v>1.8588069534310057E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="11">
+    <row r="15" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A15" s="20"/>
+      <c r="B15" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8">
         <v>0.81</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="8">
         <v>0.76</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="8">
         <v>0.73</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="8">
         <v>0.65</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="8">
         <v>0.77</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="8">
         <v>0.8</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="8">
         <v>0.73</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="8">
         <v>0.75</v>
       </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="10">
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="9">
         <f>400/(SQRT(3)*18.15)</f>
         <v>12.723972874702499</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11">
-        <f t="shared" ref="C16:J16" si="23">C13/(SQRT(3)*0.38*C15)</f>
+    <row r="16" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A16" s="20"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="8">
+        <f t="shared" ref="C16:J16" si="19">C13/(SQRT(3)*0.38*C15)</f>
         <v>15.943720884053993</v>
       </c>
-      <c r="D16" s="11">
-        <f t="shared" si="23"/>
+      <c r="D16" s="8">
+        <f t="shared" si="19"/>
         <v>8.9961087650738101</v>
       </c>
-      <c r="E16" s="11">
-        <f t="shared" si="23"/>
+      <c r="E16" s="8">
+        <f t="shared" si="19"/>
         <v>13.112136611011689</v>
       </c>
-      <c r="F16" s="11">
-        <f t="shared" si="23"/>
+      <c r="F16" s="8">
+        <f t="shared" si="19"/>
         <v>23.37450482549092</v>
       </c>
-      <c r="G16" s="11">
-        <f t="shared" si="23"/>
+      <c r="G16" s="8">
+        <f t="shared" si="19"/>
         <v>7.8926899410748561</v>
       </c>
-      <c r="H16" s="11">
-        <f t="shared" si="23"/>
+      <c r="H16" s="8">
+        <f t="shared" si="19"/>
         <v>18.991785170711374</v>
       </c>
-      <c r="I16" s="11">
-        <f t="shared" si="23"/>
+      <c r="I16" s="8">
+        <f t="shared" si="19"/>
         <v>9.3658118650083502</v>
       </c>
-      <c r="J16" s="11">
-        <f t="shared" si="23"/>
+      <c r="J16" s="8">
+        <f t="shared" si="19"/>
         <v>6.0773712546276402</v>
       </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="10"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="13"/>
     </row>
-    <row r="17" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="16"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11">
-        <f t="shared" ref="C17:J17" si="24">C16/2.7</f>
+    <row r="17" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A17" s="21"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="8">
+        <f t="shared" ref="C17:J17" si="20">C16/2.7</f>
         <v>5.9050818089088857</v>
       </c>
-      <c r="D17" s="11">
-        <f t="shared" si="24"/>
+      <c r="D17" s="8">
+        <f t="shared" si="20"/>
         <v>3.3318921352125219</v>
       </c>
-      <c r="E17" s="11">
-        <f t="shared" si="24"/>
+      <c r="E17" s="8">
+        <f t="shared" si="20"/>
         <v>4.8563468929672915</v>
       </c>
-      <c r="F17" s="11">
-        <f t="shared" si="24"/>
+      <c r="F17" s="8">
+        <f t="shared" si="20"/>
         <v>8.6572240094410802</v>
       </c>
-      <c r="G17" s="11">
-        <f t="shared" si="24"/>
+      <c r="G17" s="8">
+        <f t="shared" si="20"/>
         <v>2.9232184966943908</v>
       </c>
-      <c r="H17" s="11">
-        <f t="shared" si="24"/>
+      <c r="H17" s="8">
+        <f t="shared" si="20"/>
         <v>7.0339945076708785</v>
       </c>
-      <c r="I17" s="11">
-        <f t="shared" si="24"/>
+      <c r="I17" s="8">
+        <f t="shared" si="20"/>
         <v>3.4688192092623518</v>
       </c>
-      <c r="J17" s="11">
-        <f t="shared" si="24"/>
+      <c r="J17" s="8">
+        <f t="shared" si="20"/>
         <v>2.2508782424546814</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="10">
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="9">
         <v>0.15010000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="12">
+    <row r="18" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A18" s="19">
         <v>4</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="11">
+      <c r="B18" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="8">
         <v>4</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>10</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>4.5</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="8">
         <v>3</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="8">
         <v>5</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="8">
         <v>4.5</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="8">
         <v>6</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="8">
         <v>3.6</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="8">
         <v>4.2</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="8">
         <v>7</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="16">
         <f>(C18*C19+D18*D19+E18*E19+F18*F19+G18*G19+H18*H19+I18*I19+J18*J19+K18*K19+L18*L19)/(C18+D18+E18+F18+G18+H18+I18+J18+K18+L18)</f>
         <v>0.60666023166023164</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="19">
         <v>10</v>
       </c>
-      <c r="O18" s="13">
-        <f t="shared" ref="O18" si="25">M18+(1-M18)/SQRT(N18)</f>
+      <c r="O18" s="16">
+        <f t="shared" ref="O18" si="21">M18+(1-M18)/SQRT(N18)</f>
         <v>0.73104518788789719</v>
       </c>
-      <c r="P18" s="13">
-        <f t="shared" ref="P18" si="26">C18+D18+E18+F18+G18+H18+I18+J18+K18+L18</f>
+      <c r="P18" s="16">
+        <f t="shared" ref="P18" si="22">C18+D18+E18+F18+G18+H18+I18+J18+K18+L18</f>
         <v>51.800000000000004</v>
       </c>
-      <c r="Q18" s="13">
-        <f t="shared" ref="Q18" si="27">O18*P18</f>
+      <c r="Q18" s="16">
+        <f t="shared" ref="Q18" si="23">O18*P18</f>
         <v>37.868140732593076</v>
       </c>
-      <c r="R18" s="13">
-        <f t="shared" ref="R18" si="28">(C18*C20+D18*D20+E18*E20+F18*F20+G18*G20+H18*H20+I18*I20+J18*J20+K18*K20+L18*L20)/P18</f>
+      <c r="R18" s="16">
+        <f t="shared" ref="R18" si="24">(C18*C20+D18*D20+E18*E20+F18*F20+G18*G20+H18*H20+I18*I20+J18*J20+K18*K20+L18*L20)/P18</f>
         <v>0.76164092664092664</v>
       </c>
-      <c r="S18" s="13">
-        <f t="shared" ref="S18" si="29">SQRT(1-POWER(R18,2))/R18</f>
+      <c r="S18" s="16">
+        <f t="shared" ref="S18" si="25">SQRT(1-POWER(R18,2))/R18</f>
         <v>0.85079370345513616</v>
       </c>
-      <c r="T18" s="13">
-        <f t="shared" ref="T18" si="30">P18/R18</f>
+      <c r="T18" s="16">
+        <f t="shared" ref="T18" si="26">P18/R18</f>
         <v>68.011051124122375</v>
       </c>
-      <c r="U18" s="13">
-        <f t="shared" ref="U18" si="31">P18*S18</f>
+      <c r="U18" s="16">
+        <f t="shared" ref="U18" si="27">P18*S18</f>
         <v>44.071113838976054</v>
       </c>
-      <c r="V18" s="13">
+      <c r="V18" s="16">
         <f>C21+D21+E21+F21+G21+H21+I21+J21+K21+L21</f>
         <v>103.71512266090026</v>
       </c>
-      <c r="W18" s="13">
-        <f t="shared" ref="W18" si="32">V18/1.8</f>
-        <v>57.619512589389032</v>
-      </c>
-      <c r="X18" s="13">
-        <f t="shared" ref="X18" si="33">V18/2.7</f>
-        <v>38.413008392926024</v>
-      </c>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="10">
+      <c r="W18" s="22"/>
+      <c r="X18" s="9">
         <v>9.4000000000000004E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11">
+    <row r="19" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A19" s="20"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="8">
         <v>0.66</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="8">
         <v>0.37</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>0.67</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="8">
         <v>0.75</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="8">
         <v>0.63</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="8">
         <v>0.65</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="8">
         <v>0.72</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="8">
         <v>0.49</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="8">
         <v>0.8</v>
       </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="10">
-        <f>SQRT(POWER(Z12+Z17,2)+POWER(Z11+Z13+Z18,2))</f>
-        <v>0.15997063670329684</v>
+      <c r="M19" s="17"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="9">
+        <f>SQRT(POWER(X12+X17,2)+POWER(X11+X13+X18,2))</f>
+        <v>0.16004798792900665</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="14"/>
-      <c r="B20" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="11">
+    <row r="20" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A20" s="20"/>
+      <c r="B20" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="8">
         <v>0.77</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="8">
         <v>0.8</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <v>0.73</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="8">
         <v>0.75</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="8">
         <v>0.76</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="8">
         <v>0.8</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="8">
         <v>0.82</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="8">
         <v>0.67</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="8">
         <v>0.68</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="8">
         <v>0.75</v>
       </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="10">
+      <c r="M20" s="17"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="9">
         <f>400/(SQRT(3)*159.77)</f>
         <v>1.4454535123981367</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="14"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11">
-        <f t="shared" ref="C21:L21" si="34">C18/(SQRT(3)*0.38*C20)</f>
+    <row r="21" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A21" s="20"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="8">
+        <f t="shared" ref="C21:L21" si="28">C18/(SQRT(3)*0.38*C20)</f>
         <v>7.8926899410748561</v>
       </c>
-      <c r="D21" s="11">
-        <f t="shared" si="34"/>
+      <c r="D21" s="8">
+        <f t="shared" si="28"/>
         <v>18.991785170711374</v>
       </c>
-      <c r="E21" s="11">
-        <f t="shared" si="34"/>
+      <c r="E21" s="8">
+        <f t="shared" si="28"/>
         <v>9.3658118650083502</v>
       </c>
-      <c r="F21" s="11">
-        <f t="shared" si="34"/>
+      <c r="F21" s="8">
+        <f t="shared" si="28"/>
         <v>6.0773712546276402</v>
       </c>
-      <c r="G21" s="11">
-        <f t="shared" si="34"/>
+      <c r="G21" s="8">
+        <f t="shared" si="28"/>
         <v>9.9956764056375675</v>
       </c>
-      <c r="H21" s="11">
-        <f t="shared" si="34"/>
+      <c r="H21" s="8">
+        <f t="shared" si="28"/>
         <v>8.5463033268201194</v>
       </c>
-      <c r="I21" s="11">
-        <f t="shared" si="34"/>
+      <c r="I21" s="8">
+        <f t="shared" si="28"/>
         <v>11.117142538953001</v>
       </c>
-      <c r="J21" s="11">
-        <f t="shared" si="34"/>
+      <c r="J21" s="8">
+        <f t="shared" si="28"/>
         <v>8.1636330286042931</v>
       </c>
-      <c r="K21" s="11">
-        <f t="shared" si="34"/>
+      <c r="K21" s="8">
+        <f t="shared" si="28"/>
         <v>9.384176201998562</v>
       </c>
-      <c r="L21" s="11">
-        <f t="shared" si="34"/>
+      <c r="L21" s="8">
+        <f t="shared" si="28"/>
         <v>14.180532927464494</v>
       </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
     </row>
-    <row r="22" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11">
-        <f t="shared" ref="C22:L22" si="35">C21/2.7</f>
+    <row r="22" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A22" s="21"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="8">
+        <f t="shared" ref="C22:L22" si="29">C21/2.7</f>
         <v>2.9232184966943908</v>
       </c>
-      <c r="D22" s="11">
-        <f t="shared" si="35"/>
+      <c r="D22" s="8">
+        <f t="shared" si="29"/>
         <v>7.0339945076708785</v>
       </c>
-      <c r="E22" s="11">
-        <f t="shared" si="35"/>
+      <c r="E22" s="8">
+        <f t="shared" si="29"/>
         <v>3.4688192092623518</v>
       </c>
-      <c r="F22" s="11">
-        <f t="shared" si="35"/>
+      <c r="F22" s="8">
+        <f t="shared" si="29"/>
         <v>2.2508782424546814</v>
       </c>
-      <c r="G22" s="11">
-        <f t="shared" si="35"/>
+      <c r="G22" s="8">
+        <f t="shared" si="29"/>
         <v>3.7021023724583579</v>
       </c>
-      <c r="H22" s="11">
-        <f t="shared" si="35"/>
+      <c r="H22" s="8">
+        <f t="shared" si="29"/>
         <v>3.1652975284518958</v>
       </c>
-      <c r="I22" s="11">
-        <f t="shared" si="35"/>
+      <c r="I22" s="8">
+        <f t="shared" si="29"/>
         <v>4.1174601996122222</v>
       </c>
-      <c r="J22" s="11">
-        <f t="shared" si="35"/>
+      <c r="J22" s="8">
+        <f t="shared" si="29"/>
         <v>3.0235677883719601</v>
       </c>
-      <c r="K22" s="11">
-        <f t="shared" si="35"/>
+      <c r="K22" s="8">
+        <f t="shared" si="29"/>
         <v>3.4756208155550228</v>
       </c>
-      <c r="L22" s="11">
-        <f t="shared" si="35"/>
+      <c r="L22" s="8">
+        <f t="shared" si="29"/>
         <v>5.2520492323942563</v>
       </c>
-      <c r="M22" s="17"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9">
+        <f>(X2*5100)/8760</f>
+        <v>167.36572243666023</v>
+      </c>
     </row>
-    <row r="23" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
+    <row r="23" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A23" s="19">
         <v>5</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="11">
+      <c r="B23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="8">
         <v>7</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="8">
         <v>10</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="8">
         <v>2.8</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="8">
         <v>4.5</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="8">
         <v>6.3</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="13">
-        <f t="shared" ref="M23" si="36">(C23*C24+D23*D24+E23*E24+F23*F24+G23*G24+H23*H24+I23*I24+J23*J24)/(C23+D23+E23+F23+G23+H23+I23+J23)</f>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="16">
+        <f t="shared" ref="M23" si="30">(C23*C24+D23*D24+E23*E24+F23*F24+G23*G24+H23*H24+I23*I24+J23*J24)/(C23+D23+E23+F23+G23+H23+I23+J23)</f>
         <v>0.55205882352941171</v>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="19">
         <v>5</v>
       </c>
-      <c r="O23" s="13">
-        <f t="shared" ref="O23" si="37">M23+(1-M23)/SQRT(N23)</f>
+      <c r="O23" s="16">
+        <f t="shared" ref="O23" si="31">M23+(1-M23)/SQRT(N23)</f>
         <v>0.75238420763130465</v>
       </c>
-      <c r="P23" s="13">
-        <f t="shared" ref="P23" si="38">C23+D23+E23+F23+G23+H23+I23+J23+K23+L23</f>
+      <c r="P23" s="16">
+        <f t="shared" ref="P23" si="32">C23+D23+E23+F23+G23+H23+I23+J23+K23+L23</f>
         <v>30.6</v>
       </c>
-      <c r="Q23" s="13">
-        <f t="shared" ref="Q23" si="39">O23*P23</f>
+      <c r="Q23" s="16">
+        <f t="shared" ref="Q23" si="33">O23*P23</f>
         <v>23.022956753517924</v>
       </c>
-      <c r="R23" s="13">
-        <f t="shared" ref="R23" si="40">(C23*C25+D23*D25+E23*E25+F23*F25+G23*G25+H23*H25+I23*I25+J23*J25+K23*K25+L23*L25)/P23</f>
+      <c r="R23" s="16">
+        <f t="shared" ref="R23" si="34">(C23*C25+D23*D25+E23*E25+F23*F25+G23*G25+H23*H25+I23*I25+J23*J25+K23*K25+L23*L25)/P23</f>
         <v>0.7680065359477124</v>
       </c>
-      <c r="S23" s="13">
-        <f t="shared" ref="S23" si="41">SQRT(1-POWER(R23,2))/R23</f>
+      <c r="S23" s="16">
+        <f t="shared" ref="S23" si="35">SQRT(1-POWER(R23,2))/R23</f>
         <v>0.83390176283857753</v>
       </c>
-      <c r="T23" s="13">
-        <f t="shared" ref="T23" si="42">P23/R23</f>
+      <c r="T23" s="16">
+        <f t="shared" ref="T23" si="36">P23/R23</f>
         <v>39.843410918684313</v>
       </c>
-      <c r="U23" s="13">
-        <f t="shared" ref="U23" si="43">P23*S23</f>
+      <c r="U23" s="16">
+        <f t="shared" ref="U23" si="37">P23*S23</f>
         <v>25.517393942860473</v>
       </c>
-      <c r="V23" s="13">
+      <c r="V23" s="16">
         <f>C26+D26+E26+F26+G26+H26+I26+J26+K26+L26</f>
         <v>60.747859690298228</v>
       </c>
-      <c r="W23" s="13">
-        <f t="shared" ref="W23" si="44">V23/1.8</f>
-        <v>33.748810939054572</v>
-      </c>
-      <c r="X23" s="13">
-        <f t="shared" ref="X23" si="45">V23/2.7</f>
-        <v>22.499207292703044</v>
-      </c>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9">
+        <f>X22/X2</f>
+        <v>0.5821917808219178</v>
+      </c>
     </row>
-    <row r="24" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A24" s="14"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11">
+    <row r="24" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A24" s="20"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="8">
         <v>0.8</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="8">
         <v>0.43</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="8">
         <v>0.54</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="8">
         <v>0.47</v>
       </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="X24" s="9">
+        <v>180</v>
+      </c>
     </row>
-    <row r="25" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="11">
+    <row r="25" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A25" s="20"/>
+      <c r="B25" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="8">
         <v>0.75</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="8">
         <v>0.74</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="8">
         <v>0.69</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="8">
         <v>0.82</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="8">
         <v>0.83</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="18"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9">
+        <f>X2/X24</f>
+        <v>1.5970846716178035</v>
+      </c>
     </row>
-    <row r="26" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A26" s="14"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11">
-        <f t="shared" ref="C26:G26" si="46">C23/(SQRT(3)*0.38*C25)</f>
+    <row r="26" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A26" s="20"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="8">
+        <f t="shared" ref="C26:G26" si="38">C23/(SQRT(3)*0.38*C25)</f>
         <v>14.180532927464494</v>
       </c>
-      <c r="D26" s="11">
-        <f t="shared" si="46"/>
+      <c r="D26" s="8">
+        <f t="shared" si="38"/>
         <v>20.531659644012297</v>
       </c>
-      <c r="E26" s="11">
-        <f t="shared" si="46"/>
+      <c r="E26" s="8">
+        <f t="shared" si="38"/>
         <v>6.1654490988976054</v>
       </c>
-      <c r="F26" s="11">
-        <f t="shared" si="46"/>
+      <c r="F26" s="8">
+        <f t="shared" si="38"/>
         <v>8.3378569042147497</v>
       </c>
-      <c r="G26" s="11">
-        <f t="shared" si="46"/>
+      <c r="G26" s="8">
+        <f t="shared" si="38"/>
         <v>11.532361115709076</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
     </row>
-    <row r="27" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11">
-        <f t="shared" ref="C27:G27" si="47">C26/2.7</f>
+    <row r="27" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A27" s="21"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="8">
+        <f t="shared" ref="C27:G27" si="39">C26/2.7</f>
         <v>5.2520492323942563</v>
       </c>
-      <c r="D27" s="11">
-        <f t="shared" si="47"/>
+      <c r="D27" s="8">
+        <f t="shared" si="39"/>
         <v>7.6043183866712205</v>
       </c>
-      <c r="E27" s="11">
-        <f t="shared" si="47"/>
+      <c r="E27" s="8">
+        <f t="shared" si="39"/>
         <v>2.2834996662583724</v>
       </c>
-      <c r="F27" s="11">
-        <f t="shared" si="47"/>
+      <c r="F27" s="8">
+        <f t="shared" si="39"/>
         <v>3.0880951497091664</v>
       </c>
-      <c r="G27" s="11">
-        <f t="shared" si="47"/>
+      <c r="G27" s="8">
+        <f t="shared" si="39"/>
         <v>4.2712448576700277</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="18"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
     </row>
-    <row r="28" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
+    <row r="28" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A28" s="15">
         <v>6</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="11">
+      <c r="B28" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="8">
         <v>4.5</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="8">
         <v>10</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="8">
         <v>7.5</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="8">
         <v>10</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="8">
         <v>2.8</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="8">
         <v>5</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="8">
         <v>7.5</v>
       </c>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="9">
-        <f t="shared" ref="M28" si="48">(C28*C29+D28*D29+E28*E29+F28*F29+G28*G29+H28*H29+I28*I29+J28*J29)/(C28+D28+E28+F28+G28+H28+I28+J28)</f>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="14">
+        <f t="shared" ref="M28" si="40">(C28*C29+D28*D29+E28*E29+F28*F29+G28*G29+H28*H29+I28*I29+J28*J29)/(C28+D28+E28+F28+G28+H28+I28+J28)</f>
         <v>0.58828752642706139</v>
       </c>
-      <c r="N28" s="8">
+      <c r="N28" s="15">
         <v>7</v>
       </c>
-      <c r="O28" s="9">
-        <f t="shared" ref="O28" si="49">M28+(1-M28)/SQRT(N28)</f>
+      <c r="O28" s="14">
+        <f t="shared" ref="O28" si="41">M28+(1-M28)/SQRT(N28)</f>
         <v>0.74390021453238253</v>
       </c>
-      <c r="P28" s="9">
-        <f t="shared" ref="P28" si="50">C28+D28+E28+F28+G28+H28+I28+J28+K28+L28</f>
+      <c r="P28" s="14">
+        <f t="shared" ref="P28" si="42">C28+D28+E28+F28+G28+H28+I28+J28+K28+L28</f>
         <v>47.3</v>
       </c>
-      <c r="Q28" s="9">
-        <f t="shared" ref="Q28" si="51">O28*P28</f>
+      <c r="Q28" s="14">
+        <f t="shared" ref="Q28" si="43">O28*P28</f>
         <v>35.186480147381694</v>
       </c>
-      <c r="R28" s="9">
-        <f t="shared" ref="R28" si="52">(C28*C30+D28*D30+E28*E30+F28*F30+G28*G30+H28*H30+I28*I30+J28*J30+K28*K30+L28*L30)/P28</f>
+      <c r="R28" s="14">
+        <f t="shared" ref="R28" si="44">(C28*C30+D28*D30+E28*E30+F28*F30+G28*G30+H28*H30+I28*I30+J28*J30+K28*K30+L28*L30)/P28</f>
         <v>0.72985200845665976</v>
       </c>
-      <c r="S28" s="9">
-        <f t="shared" ref="S28" si="53">SQRT(1-POWER(R28,2))/R28</f>
+      <c r="S28" s="14">
+        <f t="shared" ref="S28" si="45">SQRT(1-POWER(R28,2))/R28</f>
         <v>0.93663533803218346</v>
       </c>
-      <c r="T28" s="9">
-        <f t="shared" ref="T28" si="54">P28/R28</f>
+      <c r="T28" s="14">
+        <f t="shared" ref="T28" si="46">P28/R28</f>
         <v>64.807658884189777</v>
       </c>
-      <c r="U28" s="9">
-        <f t="shared" ref="U28" si="55">P28*S28</f>
+      <c r="U28" s="14">
+        <f t="shared" ref="U28" si="47">P28*S28</f>
         <v>44.302851488922272</v>
       </c>
-      <c r="V28" s="9">
+      <c r="V28" s="14">
         <f>C31+D31+E31+F31+G31+H31+I31+J31+K31+L31</f>
         <v>99.265990465301741</v>
       </c>
-      <c r="W28" s="9">
-        <f t="shared" ref="W28" si="56">V28/1.8</f>
-        <v>55.147772480723191</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" ref="X28" si="57">V28/2.7</f>
-        <v>36.765181653815461</v>
-      </c>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
     </row>
-    <row r="29" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A29" s="8"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11">
+    <row r="29" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A29" s="15"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="8">
         <v>0.62</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="8">
         <v>0.46</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="8">
         <v>0.68</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="8">
         <v>0.87</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="8">
         <v>0.83</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="8">
         <v>0.38</v>
       </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="18"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
     </row>
-    <row r="30" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A30" s="8"/>
-      <c r="B30" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="11">
+    <row r="30" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A30" s="15"/>
+      <c r="B30" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="8">
         <v>0.81</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="8">
         <v>0.68</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="8">
         <v>0.64</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="8">
         <v>0.79</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="8">
         <v>0.84</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="8">
         <v>0.77</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="8">
         <v>0.69</v>
       </c>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
     </row>
-    <row r="31" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A31" s="8"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11">
-        <f t="shared" ref="C31:I31" si="58">C28/(SQRT(3)*0.38*C30)</f>
+    <row r="31" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A31" s="15"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="8">
+        <f t="shared" ref="C31:I31" si="48">C28/(SQRT(3)*0.38*C30)</f>
         <v>8.4407934092050549</v>
       </c>
-      <c r="D31" s="11">
-        <f t="shared" si="58"/>
+      <c r="D31" s="8">
+        <f t="shared" si="48"/>
         <v>22.343276671425144</v>
       </c>
-      <c r="E31" s="11">
-        <f t="shared" si="58"/>
+      <c r="E31" s="8">
+        <f t="shared" si="48"/>
         <v>17.804798597541915</v>
       </c>
-      <c r="F31" s="11">
-        <f t="shared" si="58"/>
+      <c r="F31" s="8">
+        <f t="shared" si="48"/>
         <v>19.23218751464443</v>
       </c>
-      <c r="G31" s="11">
-        <f t="shared" si="58"/>
+      <c r="G31" s="8">
+        <f t="shared" si="48"/>
         <v>5.0644760455230333</v>
       </c>
-      <c r="H31" s="11">
-        <f t="shared" si="58"/>
+      <c r="H31" s="8">
+        <f t="shared" si="48"/>
         <v>9.8658624263435701</v>
       </c>
-      <c r="I31" s="11">
-        <f t="shared" si="58"/>
+      <c r="I31" s="8">
+        <f t="shared" si="48"/>
         <v>16.514595800618586</v>
       </c>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
     </row>
-    <row r="32" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A32" s="8"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="11">
-        <f t="shared" ref="C32:I32" si="59">C31/2.7</f>
+    <row r="32" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A32" s="15"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="8">
+        <f t="shared" ref="C32:I32" si="49">C31/2.7</f>
         <v>3.1262197811870571</v>
       </c>
-      <c r="D32" s="11">
-        <f t="shared" si="59"/>
+      <c r="D32" s="8">
+        <f t="shared" si="49"/>
         <v>8.2752876560833855</v>
       </c>
-      <c r="E32" s="11">
-        <f t="shared" si="59"/>
+      <c r="E32" s="8">
+        <f t="shared" si="49"/>
         <v>6.5943698509414492</v>
       </c>
-      <c r="F32" s="11">
-        <f t="shared" si="59"/>
+      <c r="F32" s="8">
+        <f t="shared" si="49"/>
         <v>7.1230324128312699</v>
       </c>
-      <c r="G32" s="11">
-        <f t="shared" si="59"/>
+      <c r="G32" s="8">
+        <f t="shared" si="49"/>
         <v>1.8757318687122344</v>
       </c>
-      <c r="H32" s="11">
-        <f t="shared" si="59"/>
+      <c r="H32" s="8">
+        <f t="shared" si="49"/>
         <v>3.6540231208679885</v>
       </c>
-      <c r="I32" s="11">
-        <f t="shared" si="59"/>
+      <c r="I32" s="8">
+        <f t="shared" si="49"/>
         <v>6.1165169631920691</v>
       </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="93">
-    <mergeCell ref="X28:X32"/>
+  <mergeCells count="79">
     <mergeCell ref="S28:S32"/>
     <mergeCell ref="T28:T32"/>
     <mergeCell ref="U28:U32"/>
     <mergeCell ref="V28:V32"/>
-    <mergeCell ref="W28:W32"/>
-    <mergeCell ref="X18:X22"/>
     <mergeCell ref="M23:M27"/>
     <mergeCell ref="N23:N27"/>
     <mergeCell ref="O23:O27"/>
@@ -10277,19 +10074,13 @@
     <mergeCell ref="T23:T27"/>
     <mergeCell ref="U23:U27"/>
     <mergeCell ref="V23:V27"/>
-    <mergeCell ref="W23:W27"/>
-    <mergeCell ref="X23:X27"/>
     <mergeCell ref="S18:S22"/>
     <mergeCell ref="T18:T22"/>
     <mergeCell ref="U18:U22"/>
     <mergeCell ref="V18:V22"/>
-    <mergeCell ref="W18:W22"/>
     <mergeCell ref="T13:T17"/>
     <mergeCell ref="U13:U17"/>
     <mergeCell ref="V13:V17"/>
-    <mergeCell ref="W13:W17"/>
-    <mergeCell ref="X8:X12"/>
-    <mergeCell ref="X13:X17"/>
     <mergeCell ref="O13:O17"/>
     <mergeCell ref="P13:P17"/>
     <mergeCell ref="Q13:Q17"/>
@@ -10299,8 +10090,6 @@
     <mergeCell ref="T8:T12"/>
     <mergeCell ref="U8:U12"/>
     <mergeCell ref="V8:V12"/>
-    <mergeCell ref="W8:W12"/>
-    <mergeCell ref="X1:X2"/>
     <mergeCell ref="M3:M7"/>
     <mergeCell ref="N3:N7"/>
     <mergeCell ref="O3:O7"/>
@@ -10309,7 +10098,6 @@
     <mergeCell ref="R3:R7"/>
     <mergeCell ref="S3:S7"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="X3:X7"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="R1:R2"/>
@@ -10317,11 +10105,9 @@
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="W1:W2"/>
     <mergeCell ref="T3:T7"/>
     <mergeCell ref="U3:U7"/>
     <mergeCell ref="V3:V7"/>
-    <mergeCell ref="W3:W7"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:L1"/>
